--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,264 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E7" s="2">
         <v>45137</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1827000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1861000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1574000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1374000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1818000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1598000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1246500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1404800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1297600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1055000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>831800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1012500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>955900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>842100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>733200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>952100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1360000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1135000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1001000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1318000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1360000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1177000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>919100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1034200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>972400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>798000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>627600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>768100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>725300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>642900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>552400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>726100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E10" s="3">
         <v>501000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>439000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>373000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>501000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>421000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>327400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>370600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>325200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>257000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>204200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>244400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>230600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>199200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>180800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>226000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +947,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -990,8 +1004,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,19 +1063,22 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>1000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1066,24 +1086,24 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>300</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>300</v>
       </c>
       <c r="L14" s="3">
+        <v>300</v>
+      </c>
+      <c r="M14" s="3">
         <v>50400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1096,14 +1116,17 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1111,55 +1134,58 @@
         <v>37000</v>
       </c>
       <c r="E15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F15" s="3">
         <v>35000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>34000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>34900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>33500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>32800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>33100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1203,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1635000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1393000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1250000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1584000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1624000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1418000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1138200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1257600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1248200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>986000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>799200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>947800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>896400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>813400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>712000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>898500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E18" s="3">
         <v>226000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>181000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>124000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>234000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>237000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>180000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>108300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>147200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>69000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>64700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>53600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,8 +1344,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1367,232 +1401,247 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E21" s="3">
         <v>264000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>218000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>162000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>271000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>274000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>216000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>146000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>184300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>86900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>106700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>65800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E22" s="3">
         <v>22000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>36800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>36000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>35300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>35000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>33200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>33100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>29200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E23" s="3">
         <v>204000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>164000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>104000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>218000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>220000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>167000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>95600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>134200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E24" s="3">
         <v>40000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1696,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E26" s="3">
         <v>164000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>133000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>84000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>178000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>182000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>137000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>78800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>109300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>110000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>86000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>54000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>111000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>115000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>64400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1873,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1932,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1991,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,8 +2050,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2039,64 +2109,70 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>110000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>86000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>54000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>111000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>115000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>86000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>64400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2227,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>110000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>86000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>54000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>111000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>115000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>86000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>64400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E38" s="2">
         <v>45137</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2375,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,44 +2398,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E41" s="3">
         <v>20000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177000</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3">
         <v>1000</v>
       </c>
       <c r="K41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L41" s="3">
         <v>4900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>320200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2368,8 +2455,11 @@
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,44 +2514,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1215000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1231000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1098000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>955000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1273000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1264000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1113000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>884000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>946100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>832900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>716100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2480,44 +2573,47 @@
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E44" s="3">
         <v>896000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1030000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1047000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1148000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1166000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1063000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>856000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>721200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>593200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>509200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2536,44 +2632,47 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E45" s="3">
         <v>35000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2592,44 +2691,47 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2171000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2182000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2166000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2211000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2455000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2461000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2202000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1767000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1696900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1508300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1562800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2648,8 +2750,11 @@
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2704,44 +2809,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>326000</v>
+      </c>
+      <c r="E48" s="3">
         <v>314000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>299000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>280000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>268000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>267000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>252000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>246000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>249400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>226400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>227400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2760,44 +2868,47 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2334000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2363000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2334000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2330000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2359000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2351000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2361000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2386000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2414700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2314200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2013000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2816,8 +2927,11 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2986,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,41 +3045,44 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E52" s="3">
         <v>180000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>130000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>108000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>69000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>79000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2978,14 +3098,17 @@
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,44 +3163,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5067000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5039000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4929000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4909000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5190000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5148000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4894000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4434000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4380800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4053300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3803200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3096,8 +3222,11 @@
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3247,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,44 +3270,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>646000</v>
+      </c>
+      <c r="E57" s="3">
         <v>601000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>581000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>479000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>701000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>826000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>859000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>608000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>613300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>564900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>532500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3196,8 +3327,11 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3229,11 +3363,11 @@
         <v>15000</v>
       </c>
       <c r="M58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N58" s="3">
         <v>13000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3252,44 +3386,47 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E59" s="3">
         <v>226000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>202000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>232000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>271000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>238000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>192000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>216000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>214300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>164900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>148600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3308,44 +3445,47 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>921000</v>
+      </c>
+      <c r="E60" s="3">
         <v>842000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>798000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>726000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>987000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1079000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1066000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>839000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>842600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>744800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>694100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3364,44 +3504,47 @@
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1554000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1571000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1444000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1537000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1592000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1510000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1456000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1459000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1462000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2251500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3420,44 +3563,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E62" s="3">
         <v>430000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>368000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>329000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>314000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>312000</v>
       </c>
       <c r="I62" s="3">
         <v>312000</v>
       </c>
       <c r="J62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="K62" s="3">
         <v>308000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>320500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>298500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>158500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3476,8 +3622,11 @@
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3681,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3740,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,44 +3799,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3298000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3344000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3301000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3162000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3486000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3598000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3458000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3109000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3157500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2981400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3104100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3700,8 +3858,11 @@
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3883,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3940,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3999,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4058,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,41 +4117,44 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E72" s="3">
         <v>447000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>403000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>458000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>404000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>298000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>180000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>92000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>44400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3996,14 +4170,17 @@
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4235,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4294,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,44 +4353,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1769000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1695000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1628000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1747000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1704000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1550000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1436000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1325000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1223300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1071900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>699100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4226,8 +4412,11 @@
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4471,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E80" s="2">
         <v>45137</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>110000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>86000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>54000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>111000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>115000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>86000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>64400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,44 +4619,45 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E83" s="3">
         <v>38000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>37000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>37000</v>
       </c>
       <c r="H83" s="3">
         <v>37000</v>
       </c>
       <c r="I83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J83" s="3">
         <v>36000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>37700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>37100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4477,8 +4676,11 @@
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4735,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4794,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4853,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4912,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,44 +4971,47 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E89" s="3">
         <v>282000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>120000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>307000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>154000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-56600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
@@ -4813,8 +5030,11 @@
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,44 +5055,45 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-5000</v>
       </c>
       <c r="G91" s="3">
         <v>-5000</v>
       </c>
       <c r="H91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
@@ -4891,8 +5112,11 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5171,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,44 +5230,47 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-90000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-45000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-176000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5059,8 +5289,11 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5314,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5371,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5430,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5489,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,44 +5548,47 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-173000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-111000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-77000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>67000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>48000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>81400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-188000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
@@ -5361,8 +5607,11 @@
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5417,44 +5666,47 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-176000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>177000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-253600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5471,6 +5723,9 @@
         <v>8</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,277 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F7" s="2">
         <v>45228</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45137</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44955</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44864</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44682</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44591</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44409</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44318</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44136</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44045</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43954</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43863</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43772</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1741000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="F8" s="3">
         <v>1827000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1861000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1574000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1374000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1818000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1861000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1598000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1246500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1404800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1297600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1055000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>831800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1012500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>955900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>842100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>733200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>952100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1056000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1333000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1360000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1135000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1001000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1318000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1360000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1177000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>919100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1034200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>972400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>798000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>627600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>768100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>725300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>642900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>552400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>726100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>384000</v>
+      </c>
+      <c r="F10" s="3">
         <v>494000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>501000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>439000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>373000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>500000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>501000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>421000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>327400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>370600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>325200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>257000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>204200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>244400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>230600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>199200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>180800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>226000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +973,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1007,8 +1034,14 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,50 +1099,56 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F14" s="3">
         <v>1000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>50400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1119,73 +1158,85 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>38000</v>
+      </c>
+      <c r="F15" s="3">
         <v>37000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>37000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>35000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>36000</v>
       </c>
       <c r="H15" s="3">
         <v>35000</v>
       </c>
       <c r="I15" s="3">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="J15" s="3">
         <v>35000</v>
       </c>
       <c r="K15" s="3">
+        <v>34000</v>
+      </c>
+      <c r="L15" s="3">
+        <v>35000</v>
+      </c>
+      <c r="M15" s="3">
         <v>35400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>35200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>33600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>34000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>34600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>34900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>34300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>33500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>32800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>33100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,126 +1255,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1573000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1610000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1635000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1393000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1250000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1584000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1624000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1418000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1138200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1257600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1248200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>986000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>799200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>947800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>896400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>813400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>712000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>898500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>116000</v>
+      </c>
+      <c r="F18" s="3">
         <v>217000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>226000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>181000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>124000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>234000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>237000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>180000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>108300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>147200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>49400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>69000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>32600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>64700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>59500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>28700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>21200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>53600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,8 +1410,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1404,244 +1471,274 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>156000</v>
+      </c>
+      <c r="F21" s="3">
         <v>256000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>264000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>218000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>162000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>271000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>274000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>216000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>146000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>184300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>86900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>106700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>65800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20000</v>
+        <v>34000</v>
       </c>
       <c r="E22" s="3">
         <v>22000</v>
       </c>
       <c r="F22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="H22" s="3">
         <v>17000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>20000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>16000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>17000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>13000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>12700</v>
       </c>
       <c r="L22" s="3">
         <v>13000</v>
       </c>
       <c r="M22" s="3">
+        <v>12700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O22" s="3">
         <v>36800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>36000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>35300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>35600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>35000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>33200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>33100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>29200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F23" s="3">
         <v>197000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>204000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>164000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>104000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>218000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>220000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>167000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>95600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>134200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>12600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>33000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>29100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>24500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-11900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>24400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>40000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>31000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>20000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>40000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>38000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>30000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>16800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>24900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
+        <v>400</v>
+      </c>
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,126 +1796,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>76000</v>
+      </c>
+      <c r="F26" s="3">
         <v>158000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>164000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>133000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>84000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>178000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>182000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>137000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>78800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>109300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>27000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>26200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>24100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-12300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>24600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>110000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>86000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>54000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>111000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>115000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>86000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>47700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>64400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>26500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>27000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>26200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>24100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-12300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>24600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1991,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1935,8 +2056,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2121,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,8 +2186,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2112,67 +2251,79 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F33" s="3">
         <v>112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>110000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>86000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>54000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>111000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>115000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>86000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>47700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>64400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>26500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>27000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>26200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>24100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-12300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>24600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,131 +2381,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F35" s="3">
         <v>112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>110000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>86000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>54000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>111000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>115000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>86000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>47700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>64400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>26500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>27000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>26200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>24100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-12300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>24600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F38" s="2">
         <v>45228</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45137</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44955</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44864</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44682</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44591</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44409</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44318</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44136</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44045</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43954</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43863</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43772</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2545,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,50 +2570,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="3">
         <v>101000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>20000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>177000</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>66600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>320200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2458,8 +2631,14 @@
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2517,50 +2696,56 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>973000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1215000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1231000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1098000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>955000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1273000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1264000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1113000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>884000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>946100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>832900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>716100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2576,50 +2761,56 @@
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>945000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>766000</v>
+      </c>
+      <c r="F44" s="3">
         <v>824000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>896000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1030000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1047000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1148000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1166000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1063000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>856000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>721200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>593200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>509200</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2635,50 +2826,56 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F45" s="3">
         <v>31000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>35000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>37000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>32000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>34000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>31000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>25000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>26000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>24700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>15600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>17300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2694,50 +2891,56 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2223000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2171000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2182000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2166000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2211000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2455000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2461000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2202000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1767000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1696900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1508300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1562800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2753,8 +2956,14 @@
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2812,50 +3021,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>343000</v>
+      </c>
+      <c r="F48" s="3">
         <v>326000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>314000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>299000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>280000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>268000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>267000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>252000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>246000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>249400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>226400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>227400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2871,50 +3086,56 @@
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2334000</v>
+        <v>2816000</v>
       </c>
       <c r="E49" s="3">
-        <v>2363000</v>
+        <v>2345000</v>
       </c>
       <c r="F49" s="3">
         <v>2334000</v>
       </c>
       <c r="G49" s="3">
+        <v>2363000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2334000</v>
+      </c>
+      <c r="I49" s="3">
         <v>2330000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2359000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2351000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2361000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2386000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2414700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2314200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2013000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2930,8 +3151,14 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3216,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,47 +3281,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>608000</v>
+      </c>
+      <c r="F52" s="3">
         <v>236000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>180000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>130000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>88000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>108000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>69000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>79000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>35000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>19800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3101,14 +3340,20 @@
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,50 +3411,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6041000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5069000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5067000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5039000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4929000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4909000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5190000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5148000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4894000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4434000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4380800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4053300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3803200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3225,8 +3476,14 @@
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3505,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,50 +3530,52 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>777000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>504000</v>
+      </c>
+      <c r="F57" s="3">
         <v>646000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>601000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>581000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>479000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>701000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>826000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>859000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>608000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>613300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>564900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>532500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3330,13 +3591,19 @@
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="E58" s="3">
         <v>15000</v>
@@ -3366,14 +3633,14 @@
         <v>15000</v>
       </c>
       <c r="N58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P58" s="3">
         <v>13000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3389,50 +3656,56 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>255000</v>
+      </c>
+      <c r="F59" s="3">
         <v>260000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>226000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>202000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>232000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>271000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>238000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>192000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>216000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>214300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>164900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>148600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3448,50 +3721,56 @@
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>774000</v>
+      </c>
+      <c r="F60" s="3">
         <v>921000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>842000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>798000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>726000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>987000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1079000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1066000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>839000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>842600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>744800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>694100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3507,50 +3786,56 @@
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2401000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1863000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1436000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1554000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1571000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1444000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1537000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1592000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1510000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1456000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1459000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1462000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2251500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3566,50 +3851,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>958000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>908000</v>
+      </c>
+      <c r="F62" s="3">
         <v>495000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>430000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>368000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>329000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>314000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>312000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>312000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>308000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>320500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>298500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>158500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3625,8 +3916,14 @@
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3981,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +4046,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,50 +4111,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4471000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3618000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3298000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3344000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3301000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3162000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3486000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3598000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3458000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3109000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3157500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2981400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3104100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3861,8 +4176,14 @@
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4205,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4266,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4331,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4061,8 +4396,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,47 +4461,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>189000</v>
+      </c>
+      <c r="F72" s="3">
         <v>491000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>447000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>403000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>458000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>404000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>298000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>180000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>92000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>44400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-20000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4173,14 +4520,20 @@
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4591,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4656,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,50 +4721,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1570000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1769000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1695000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1628000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1747000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1704000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1550000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1436000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1325000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1223300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1071900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>699100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4415,8 +4786,14 @@
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,131 +4851,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45410</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45319</v>
+      </c>
+      <c r="F80" s="2">
         <v>45228</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45137</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44955</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44864</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44682</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44591</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44409</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44318</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44136</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44045</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43954</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43863</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43772</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F81" s="3">
         <v>112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>110000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>86000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>54000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>111000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>115000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>86000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>47700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>64400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>26500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>27000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>26200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>24100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-12300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>24600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,19 +5015,21 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F83" s="3">
         <v>39000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>38000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>37000</v>
       </c>
       <c r="G83" s="3">
         <v>38000</v>
@@ -4641,29 +5038,29 @@
         <v>37000</v>
       </c>
       <c r="I83" s="3">
+        <v>38000</v>
+      </c>
+      <c r="J83" s="3">
         <v>37000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="L83" s="3">
         <v>36000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>37700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>37100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>37500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>37700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4679,8 +5076,14 @@
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +5141,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5206,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5271,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5336,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,50 +5401,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>294000</v>
+      </c>
+      <c r="F89" s="3">
         <v>373000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>282000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>120000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>307000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>154000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-23000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-37000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>35200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>32900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-56600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-42500</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5033,8 +5466,14 @@
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,50 +5495,52 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-19000</v>
+        <v>-7000</v>
       </c>
       <c r="E91" s="3">
         <v>-5000</v>
       </c>
       <c r="F91" s="3">
-        <v>-10000</v>
+        <v>-19000</v>
       </c>
       <c r="G91" s="3">
         <v>-5000</v>
       </c>
       <c r="H91" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-6000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-8000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5115,8 +5556,14 @@
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5621,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,50 +5686,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-574000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-90000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-74000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-19000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-77000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-45000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-176000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5292,8 +5751,14 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5780,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5374,8 +5841,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5906,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5971,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,50 +6036,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-274000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-173000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-111000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-77000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>67000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>48000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-25100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>81400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-188000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-14300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
@@ -5610,8 +6101,14 @@
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5669,50 +6166,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="F102" s="3">
         <v>81000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-176000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>177000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-61700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-253600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-60700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5726,6 +6229,12 @@
         <v>8</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,302 +656,315 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E7" s="2">
         <v>45410</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45319</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45228</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45137</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44955</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44864</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44682</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44591</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44409</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44318</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44136</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44045</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43954</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43863</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43772</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1741000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1440000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1827000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1861000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1574000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1374000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1818000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1861000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1598000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1246500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1404800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1297600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1055000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>831800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1012500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>955900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>842100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>733200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>952100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1446000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1273000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1056000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1333000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1360000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1135000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1001000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1318000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1360000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1177000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>919100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1034200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>972400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>798000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>627600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>768100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>725300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>642900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>552400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>726100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E10" s="3">
         <v>468000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>384000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>494000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>501000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>439000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>373000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>500000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>501000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>421000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>327400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>370600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>325200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>257000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>204200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>244400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>230600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>199200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>180800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>226000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +988,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,8 +1054,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1122,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1114,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1000</v>
       </c>
       <c r="G14" s="3">
         <v>1000</v>
@@ -1126,7 +1146,7 @@
         <v>1000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1134,24 +1154,24 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>300</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
       </c>
       <c r="O14" s="3">
+        <v>300</v>
+      </c>
+      <c r="P14" s="3">
         <v>50400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1164,79 +1184,85 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E15" s="3">
         <v>43000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>37000</v>
       </c>
       <c r="G15" s="3">
         <v>37000</v>
       </c>
       <c r="H15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I15" s="3">
         <v>35000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>33500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>32800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>33100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1283,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1760000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1573000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1324000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1610000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1635000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1393000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1250000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1584000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1624000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1418000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1138200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1257600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1248200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>986000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>799200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>947800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>896400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>813400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>712000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>898500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E18" s="3">
         <v>168000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>116000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>217000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>226000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>181000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>124000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>234000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>237000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>180000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>108300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>147200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>69000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>64700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>59500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>53600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1445,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1477,268 +1511,283 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E21" s="3">
         <v>214000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>156000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>256000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>264000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>218000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>162000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>271000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>274000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>216000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>146000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>184300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>86900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>106700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>65800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>36800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>36000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>35300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>35000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>33200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>33100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>29200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E23" s="3">
         <v>134000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>197000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>204000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>164000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>104000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>218000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>220000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>167000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>95600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>134200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>29100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E24" s="3">
         <v>33000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1851,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E26" s="3">
         <v>101000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>76000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>158000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>164000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>133000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>84000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>178000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>182000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>137000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>78800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>109300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E27" s="3">
         <v>95000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>63000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>110000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>86000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>111000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>115000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>86000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>47700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>64400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2055,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2123,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2259,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2257,73 +2327,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E33" s="3">
         <v>95000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>63000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>110000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>86000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>111000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>115000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>86000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>47700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>64400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2463,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E35" s="3">
         <v>95000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>63000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>110000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>86000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>111000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>115000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>86000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>47700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>64400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E38" s="2">
         <v>45410</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45319</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45228</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45137</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44955</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44864</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44682</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44591</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44409</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44318</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44136</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44045</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43954</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43863</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43772</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,53 +2658,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E41" s="3">
         <v>30000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>177000</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
         <v>1000</v>
       </c>
       <c r="N41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O41" s="3">
         <v>4900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>66600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>320200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2637,8 +2724,11 @@
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,53 +2792,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1294000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>973000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1215000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1231000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1098000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>955000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1273000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1264000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1113000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>884000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>946100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>832900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>716100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2767,53 +2860,56 @@
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>959000</v>
+      </c>
+      <c r="E44" s="3">
         <v>945000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>766000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>824000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>896000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1030000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1047000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1148000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1166000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1063000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>856000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>721200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>593200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>509200</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2832,53 +2928,56 @@
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E45" s="3">
         <v>48000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2897,53 +2996,56 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2318000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2223000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1773000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2171000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2182000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2166000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2211000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2455000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2461000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2202000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1767000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1696900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1508300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1562800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2962,8 +3064,11 @@
       <c r="W46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3027,53 +3132,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E48" s="3">
         <v>366000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>343000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>326000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>314000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>299000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>280000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>268000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>267000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>252000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>246000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>249400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>226400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>227400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3092,53 +3200,56 @@
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2797000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2816000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2345000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2334000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2363000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2334000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2330000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2359000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2351000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2361000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2386000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2414700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2314200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2013000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3157,8 +3268,11 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,50 +3404,53 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E52" s="3">
         <v>636000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>608000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>236000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>180000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>130000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>108000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>69000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>79000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3346,14 +3466,17 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,53 +3540,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6098000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6041000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5069000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5067000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5039000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4929000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4909000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5190000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5148000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4894000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4434000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4380800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4053300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3803200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3482,8 +3608,11 @@
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,53 +3662,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>738000</v>
+      </c>
+      <c r="E57" s="3">
         <v>777000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>504000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>646000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>601000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>581000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>479000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>701000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>826000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>859000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>608000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>613300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>564900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>532500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3597,8 +3728,11 @@
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3606,7 +3740,7 @@
         <v>23000</v>
       </c>
       <c r="E58" s="3">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="F58" s="3">
         <v>15000</v>
@@ -3639,11 +3773,11 @@
         <v>15000</v>
       </c>
       <c r="P58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>13000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3662,53 +3796,56 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E59" s="3">
         <v>238000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>255000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>260000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>226000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>202000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>232000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>271000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>238000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>192000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>216000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>214300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>164900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>148600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3727,53 +3864,56 @@
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1038000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>774000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>921000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>842000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>798000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>726000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>987000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1079000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1066000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>839000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>842600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>744800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>694100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3792,53 +3932,56 @@
       <c r="W60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2404000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2401000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1863000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1436000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1554000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1571000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1444000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1537000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1592000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1510000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1456000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1459000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1462000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2251500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3857,53 +4000,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>962000</v>
+      </c>
+      <c r="E62" s="3">
         <v>958000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>908000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>495000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>430000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>368000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>329000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>314000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>312000</v>
       </c>
       <c r="L62" s="3">
         <v>312000</v>
       </c>
       <c r="M62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="N62" s="3">
         <v>308000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>320500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>298500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>158500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3922,8 +4068,11 @@
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,53 +4272,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4454000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4471000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3618000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3298000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3344000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3301000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3162000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3486000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3598000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3458000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3109000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3157500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2981400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3104100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4182,8 +4340,11 @@
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,50 +4638,53 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>385000</v>
+      </c>
+      <c r="E72" s="3">
         <v>284000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>189000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>491000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>447000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>403000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>458000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>404000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>298000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>180000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>92000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>44400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4526,14 +4700,17 @@
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,53 +4910,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1644000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1570000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1451000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1769000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1695000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1628000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1747000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1704000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1550000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1436000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1325000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1223300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1071900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>699100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4792,8 +4978,11 @@
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5046,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45501</v>
+      </c>
+      <c r="E80" s="2">
         <v>45410</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45319</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45228</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45137</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44955</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44864</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44682</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44591</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44409</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44318</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44136</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44045</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43954</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43863</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43772</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E81" s="3">
         <v>95000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>63000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>110000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>86000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>111000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>115000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>86000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>47700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>64400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,53 +5215,54 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>37000</v>
       </c>
       <c r="K83" s="3">
         <v>37000</v>
       </c>
       <c r="L83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="M83" s="3">
         <v>36000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5082,8 +5281,11 @@
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,53 +5621,56 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E89" s="3">
         <v>78000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>294000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>373000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>282000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>120000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>307000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>154000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-56600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5472,8 +5689,11 @@
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,53 +5717,54 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-5000</v>
       </c>
       <c r="J91" s="3">
         <v>-5000</v>
       </c>
       <c r="K91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5562,8 +5783,11 @@
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,53 +5919,56 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-574000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-90000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-74000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-176000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5757,8 +5987,11 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6015,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,53 +6285,56 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E100" s="3">
         <v>525000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-306000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-274000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-173000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-222000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-111000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-77000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>67000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>48000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>81400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-188000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6107,8 +6353,11 @@
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,53 +6421,56 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>29000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>81000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-176000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>177000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-61700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-253600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6235,6 +6487,9 @@
         <v>8</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,315 +656,328 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E7" s="2">
         <v>45501</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45410</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45319</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45228</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45137</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44955</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44864</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44682</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44591</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44409</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44318</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44136</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44045</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43954</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43863</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43772</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2038000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1964000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1741000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1440000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1827000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1574000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1374000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1818000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1861000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1598000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1246500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1404800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1297600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1055000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>831800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1012500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>955900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>842100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>733200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>952100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1495000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1446000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1273000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1056000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1333000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1360000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1135000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1001000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1318000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1360000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1177000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>919100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1034200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>972400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>798000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>627600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>768100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>725300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>642900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>552400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>726100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>543000</v>
+      </c>
+      <c r="E10" s="3">
         <v>518000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>468000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>384000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>494000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>501000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>439000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>373000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>500000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>501000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>421000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>327400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>370600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>325200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>257000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>204200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>244400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>230600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>199200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>180800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>226000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,8 +1002,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1071,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,31 +1142,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2000</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1157,24 +1177,24 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
-        <v>300</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>300</v>
       </c>
       <c r="P14" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="3">
         <v>50400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1187,14 +1207,17 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1202,67 +1225,70 @@
         <v>46000</v>
       </c>
       <c r="E15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F15" s="3">
         <v>43000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>38000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>37000</v>
       </c>
       <c r="H15" s="3">
         <v>37000</v>
       </c>
       <c r="I15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J15" s="3">
         <v>35000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>33600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>34300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>33500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>32800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>33100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,144 +1310,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1815000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1760000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1573000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1324000</v>
-      </c>
       <c r="G17" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="H17" s="3">
         <v>1610000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1635000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1393000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1250000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1584000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1624000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1418000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1138200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1257600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1248200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>986000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>799200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>947800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>896400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>813400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>712000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>898500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E18" s="3">
         <v>204000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>168000</v>
       </c>
-      <c r="F18" s="3">
-        <v>116000</v>
-      </c>
       <c r="G18" s="3">
+        <v>121000</v>
+      </c>
+      <c r="H18" s="3">
         <v>217000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>226000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>181000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>124000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>234000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>237000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>180000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>108300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>147200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>69000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>64700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>28700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>53600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,31 +1479,32 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1514,76 +1548,82 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>253000</v>
+        <v>269000</v>
       </c>
       <c r="E21" s="3">
-        <v>214000</v>
+        <v>250000</v>
       </c>
       <c r="F21" s="3">
-        <v>156000</v>
+        <v>211000</v>
       </c>
       <c r="G21" s="3">
-        <v>256000</v>
+        <v>159000</v>
       </c>
       <c r="H21" s="3">
-        <v>264000</v>
+        <v>254000</v>
       </c>
       <c r="I21" s="3">
-        <v>218000</v>
+        <v>263000</v>
       </c>
       <c r="J21" s="3">
+        <v>216000</v>
+      </c>
+      <c r="K21" s="3">
         <v>162000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>271000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>274000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>216000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>146000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>184300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>86900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>106700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>65800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1591,203 +1631,212 @@
         <v>36000</v>
       </c>
       <c r="E22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>36800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>35600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>33200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>33100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>29200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E23" s="3">
         <v>168000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>134000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>197000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>204000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>164000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>104000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>218000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>220000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>167000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>95600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>134200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>29100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E24" s="3">
         <v>42000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>33000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>30000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1903,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E26" s="3">
         <v>126000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>101000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>158000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>164000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>133000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>84000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>178000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>182000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>137000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>78800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>109300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E27" s="3">
         <v>119000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>95000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>63000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>110000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>111000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>115000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>86000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>47700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>64400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>26200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2116,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2187,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2258,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,31 +2329,34 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2330,76 +2400,82 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E33" s="3">
         <v>119000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>95000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>110000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>86000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>111000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>115000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>86000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>47700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>64400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2542,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E35" s="3">
         <v>119000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>95000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>110000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>86000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>111000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>115000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>86000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>47700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>64400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E38" s="2">
         <v>45501</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45410</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45319</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45228</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45137</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44955</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44864</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44682</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44591</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44409</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44318</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44136</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44045</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43954</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43863</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43772</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2718,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,56 +2745,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>177000</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
         <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
         <v>1000</v>
       </c>
       <c r="O41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P41" s="3">
         <v>4900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>320200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2727,8 +2814,11 @@
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,56 +2885,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1378000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1294000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>973000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1215000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1231000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1098000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>955000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1273000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1264000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1113000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>884000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>946100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>832900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>716100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2863,56 +2956,59 @@
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>950000</v>
+      </c>
+      <c r="E44" s="3">
         <v>959000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>945000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>766000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>824000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>896000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1030000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1047000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1148000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1166000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1063000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>856000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>721200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>593200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>509200</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2931,56 +3027,59 @@
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>52000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>48000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>33000</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>32000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>34000</v>
+      </c>
+      <c r="M45" s="3">
         <v>31000</v>
       </c>
-      <c r="H45" s="3">
-        <v>35000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>37000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>32000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>34000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>31000</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2999,56 +3098,59 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2381000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2318000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2223000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1773000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2171000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2182000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2166000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2211000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2455000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2461000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2202000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1767000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1696900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1508300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1562800</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3067,31 +3169,34 @@
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3135,56 +3240,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E48" s="3">
         <v>369000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>366000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>343000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>326000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>314000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>299000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>280000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>268000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>267000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>252000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>246000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>249400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>226400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>227400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3203,56 +3311,59 @@
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2848000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2797000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2816000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2345000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2334000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2363000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2334000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2330000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2359000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2351000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2361000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2386000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2414700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2314200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2013000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3271,8 +3382,11 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3453,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,53 +3524,56 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>614000</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
-        <v>636000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>608000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>236000</v>
+        <v>1000</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
-        <v>180000</v>
+        <v>3000</v>
       </c>
       <c r="I52" s="3">
-        <v>130000</v>
+        <v>4000</v>
       </c>
       <c r="J52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K52" s="3">
         <v>88000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>108000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>69000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>79000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3469,14 +3589,17 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,56 +3666,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6215000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6098000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6041000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5069000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5067000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5039000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4929000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4909000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5190000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5148000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4894000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4434000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4380800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4053300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3803200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3611,8 +3737,11 @@
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3766,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,56 +3793,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>782000</v>
+      </c>
+      <c r="E57" s="3">
         <v>738000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>777000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>504000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>646000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>601000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>581000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>479000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>701000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>826000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>859000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>608000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>613300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>564900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>532500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3731,31 +3862,34 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>23000</v>
+        <v>95000</v>
       </c>
       <c r="E58" s="3">
-        <v>23000</v>
+        <v>91000</v>
       </c>
       <c r="F58" s="3">
-        <v>15000</v>
+        <v>84000</v>
       </c>
       <c r="G58" s="3">
-        <v>15000</v>
+        <v>70000</v>
       </c>
       <c r="H58" s="3">
-        <v>15000</v>
+        <v>69000</v>
       </c>
       <c r="I58" s="3">
-        <v>15000</v>
+        <v>71000</v>
       </c>
       <c r="J58" s="3">
-        <v>15000</v>
+        <v>70000</v>
       </c>
       <c r="K58" s="3">
         <v>15000</v>
@@ -3776,11 +3910,11 @@
         <v>15000</v>
       </c>
       <c r="Q58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R58" s="3">
         <v>13000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3799,56 +3933,59 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>251000</v>
+        <v>125000</v>
       </c>
       <c r="E59" s="3">
+        <v>103000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>109000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>94000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>106000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>87000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>232000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>271000</v>
+      </c>
+      <c r="M59" s="3">
         <v>238000</v>
       </c>
-      <c r="F59" s="3">
-        <v>255000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>260000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>226000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>202000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>232000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>271000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>238000</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>192000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>216000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>214300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>164900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>148600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3867,56 +4004,59 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1114000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1012000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1038000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>774000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>921000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>842000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>798000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>726000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>987000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1079000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1066000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>839000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>842600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>744800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>694100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3935,56 +4075,59 @@
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2404000</v>
+        <v>2542000</v>
       </c>
       <c r="E61" s="3">
-        <v>2401000</v>
+        <v>2550000</v>
       </c>
       <c r="F61" s="3">
-        <v>1863000</v>
+        <v>2546000</v>
       </c>
       <c r="G61" s="3">
-        <v>1436000</v>
+        <v>2001000</v>
       </c>
       <c r="H61" s="3">
-        <v>1554000</v>
+        <v>1566000</v>
       </c>
       <c r="I61" s="3">
-        <v>1571000</v>
+        <v>1683000</v>
       </c>
       <c r="J61" s="3">
+        <v>1694000</v>
+      </c>
+      <c r="K61" s="3">
         <v>1444000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1537000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1592000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1510000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1456000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1459000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1462000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2251500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4003,56 +4146,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>962000</v>
+        <v>724000</v>
       </c>
       <c r="E62" s="3">
-        <v>958000</v>
+        <v>732000</v>
       </c>
       <c r="F62" s="3">
-        <v>908000</v>
+        <v>721000</v>
       </c>
       <c r="G62" s="3">
-        <v>495000</v>
+        <v>722000</v>
       </c>
       <c r="H62" s="3">
-        <v>430000</v>
+        <v>317000</v>
       </c>
       <c r="I62" s="3">
-        <v>368000</v>
+        <v>253000</v>
       </c>
       <c r="J62" s="3">
+        <v>205000</v>
+      </c>
+      <c r="K62" s="3">
         <v>329000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>314000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>312000</v>
       </c>
       <c r="M62" s="3">
         <v>312000</v>
       </c>
       <c r="N62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="O62" s="3">
         <v>308000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>320500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>298500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>158500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4071,8 +4217,11 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4288,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4359,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,56 +4430,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4454000</v>
+        <v>4465000</v>
       </c>
       <c r="E66" s="3">
-        <v>4471000</v>
+        <v>4378000</v>
       </c>
       <c r="F66" s="3">
-        <v>3618000</v>
+        <v>4397000</v>
       </c>
       <c r="G66" s="3">
-        <v>3298000</v>
+        <v>3545000</v>
       </c>
       <c r="H66" s="3">
-        <v>3344000</v>
+        <v>2852000</v>
       </c>
       <c r="I66" s="3">
-        <v>3301000</v>
+        <v>2826000</v>
       </c>
       <c r="J66" s="3">
+        <v>2737000</v>
+      </c>
+      <c r="K66" s="3">
         <v>3162000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3486000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3598000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3458000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3109000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3157500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2981400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3104100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4343,8 +4501,11 @@
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4530,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4599,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4670,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4741,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,53 +4812,56 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>433000</v>
+      </c>
+      <c r="E72" s="3">
         <v>385000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>284000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>189000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>491000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>447000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>403000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>458000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>404000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>298000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>180000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>92000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>44400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4703,14 +4877,17 @@
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4954,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5025,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,56 +5096,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1644000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1570000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1451000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1769000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1695000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1628000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1747000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1704000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1550000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1436000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1325000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1223300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1071900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>699100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4981,8 +5167,11 @@
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5238,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45592</v>
+      </c>
+      <c r="E80" s="2">
         <v>45501</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45410</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45319</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45228</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45137</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44955</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44864</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44682</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44591</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44409</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44318</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44136</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44045</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43954</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43863</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43772</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E81" s="3">
         <v>119000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>95000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>110000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>86000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>111000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>115000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>86000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>47700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>64400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,56 +5414,57 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49000</v>
+        <v>8000</v>
       </c>
       <c r="E83" s="3">
-        <v>46000</v>
+        <v>7000</v>
       </c>
       <c r="F83" s="3">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="G83" s="3">
-        <v>39000</v>
+        <v>7000</v>
       </c>
       <c r="H83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K83" s="3">
         <v>38000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>37000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>38000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>37000</v>
       </c>
       <c r="L83" s="3">
         <v>37000</v>
       </c>
       <c r="M83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="N83" s="3">
         <v>36000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5284,8 +5483,11 @@
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5554,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5625,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5696,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5767,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,56 +5838,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E89" s="3">
         <v>48000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>78000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>294000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>373000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>282000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>120000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>307000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>154000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-42500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5692,8 +5909,11 @@
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,56 +5938,57 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-5000</v>
       </c>
       <c r="K91" s="3">
         <v>-5000</v>
       </c>
       <c r="L91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5786,8 +6007,11 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6078,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,56 +6149,59 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-574000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-90000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-74000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-77000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-176000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5990,8 +6220,11 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,31 +6249,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6084,8 +6318,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6389,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6460,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,56 +6531,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>525000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-306000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-274000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-173000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-222000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-111000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-77000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>67000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>48000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>81400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6356,31 +6602,34 @@
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6424,56 +6673,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>81000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-176000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>177000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-61700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-253600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6490,6 +6742,9 @@
         <v>8</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45592</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45501</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45410</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45319</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45228</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45137</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44955</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44864</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44682</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44591</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44409</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44318</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44136</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44045</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43954</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43863</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43772</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1698000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2038000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1964000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1741000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1440000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1827000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1861000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1574000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1374000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1818000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1861000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1598000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1246500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1404800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1297600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1055000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>831800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1012500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>955900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>842100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>733200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>952100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1495000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1446000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1273000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1056000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1333000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1360000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1135000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1001000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1318000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1360000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1177000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>919100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1034200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>972400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>798000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>627600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>768100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>725300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>642900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>552400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>726100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>451000</v>
+      </c>
+      <c r="E10" s="3">
         <v>543000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>518000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>468000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>384000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>494000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>501000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>439000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>373000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>500000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>501000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>421000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>327400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>370600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>325200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>257000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>204200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>244400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>230600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>199200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>180800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>226000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,8 +1016,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1074,8 +1088,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1145,8 +1162,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1159,8 +1179,8 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>5000</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1171,8 +1191,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1180,24 +1200,24 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>300</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>300</v>
       </c>
       <c r="Q14" s="3">
+        <v>300</v>
+      </c>
+      <c r="R14" s="3">
         <v>50400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1210,85 +1230,91 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>46000</v>
+        <v>48000</v>
       </c>
       <c r="E15" s="3">
         <v>46000</v>
       </c>
       <c r="F15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="G15" s="3">
         <v>43000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>38000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>37000</v>
       </c>
       <c r="I15" s="3">
         <v>37000</v>
       </c>
       <c r="J15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K15" s="3">
         <v>35000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>33600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>34900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>33500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>32800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>33100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1574000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1815000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1760000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1573000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1319000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1610000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1635000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1393000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1250000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1584000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1624000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1418000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1138200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1257600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1248200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>986000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>799200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>947800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>896400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>813400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>712000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>898500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E18" s="3">
         <v>223000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>204000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>168000</v>
       </c>
-      <c r="G18" s="3">
-        <v>121000</v>
-      </c>
       <c r="H18" s="3">
+        <v>116000</v>
+      </c>
+      <c r="I18" s="3">
         <v>217000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>226000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>181000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>124000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>234000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>237000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>180000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>108300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>147200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>49400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>69000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>64700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>28700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>53600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,8 +1513,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1506,8 +1540,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1551,79 +1585,85 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E21" s="3">
         <v>269000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>250000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>211000</v>
       </c>
-      <c r="G21" s="3">
-        <v>159000</v>
-      </c>
       <c r="H21" s="3">
+        <v>154000</v>
+      </c>
+      <c r="I21" s="3">
         <v>254000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>263000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>216000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>162000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>271000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>274000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>216000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>146000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>184300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>86900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>106700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>65800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1634,209 +1674,218 @@
         <v>36000</v>
       </c>
       <c r="F22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="G22" s="3">
         <v>34000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>36000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>35300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>35000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>33200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>33100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>29200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E23" s="3">
         <v>187000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>168000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>134000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>197000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>204000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>164000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>104000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>218000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>220000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>167000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>95600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>134200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="3">
         <v>47000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>42000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>40000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>30000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E26" s="3">
         <v>140000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>126000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>101000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>76000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>158000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>164000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>133000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>84000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>178000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>182000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>137000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>78800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>109300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-12300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E27" s="3">
         <v>133000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>119000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>95000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>63000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>112000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>110000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>86000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>111000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>115000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>86000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>47700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>64400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2190,8 +2251,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,8 +2399,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2358,8 +2428,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2403,79 +2473,85 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E33" s="3">
         <v>133000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>119000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>95000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>63000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>112000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>110000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>86000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>111000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>115000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>86000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>47700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>64400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E35" s="3">
         <v>133000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>119000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>95000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>63000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>112000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>110000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>86000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>111000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>115000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>86000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>47700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>64400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45592</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45501</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45410</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45319</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45228</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45137</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44955</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44864</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44682</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44591</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44409</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44318</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44136</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44045</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43954</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43863</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43772</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,59 +2832,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>101000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>177000</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3">
         <v>1000</v>
       </c>
       <c r="P41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q41" s="3">
         <v>4900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>320200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2817,8 +2904,11 @@
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2888,59 +2978,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1066000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1378000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1294000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>973000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1215000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1231000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1098000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>955000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1273000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1264000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1113000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>884000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>946100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>832900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>716100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2959,59 +3052,62 @@
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>908000</v>
+      </c>
+      <c r="E44" s="3">
         <v>950000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>959000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>945000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>766000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>824000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>896000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1030000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1047000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1148000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1166000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1063000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>856000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>721200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>593200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>509200</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3030,8 +3126,11 @@
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3056,33 +3155,33 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>32000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3101,59 +3200,62 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2025000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2381000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2318000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2223000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1773000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2171000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2182000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2166000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2211000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2455000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2461000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2202000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1767000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1696900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1508300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1562800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3172,35 +3274,38 @@
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E47" s="3">
         <v>44000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>54000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>91000</v>
       </c>
-      <c r="G47" s="3">
-        <v>67000</v>
-      </c>
       <c r="H47" s="3">
+        <v>66000</v>
+      </c>
+      <c r="I47" s="3">
         <v>82000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>85000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>76000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3243,59 +3348,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E48" s="3">
         <v>387000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>369000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>366000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>343000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>326000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>314000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>299000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>280000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>268000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>267000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>252000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>246000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>249400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>226400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>227400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3314,59 +3422,62 @@
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2833000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2848000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2797000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2816000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2345000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2334000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2363000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2334000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2330000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2359000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2351000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2361000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2386000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2414700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2314200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2013000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3385,8 +3496,11 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,56 +3644,59 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>88000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>108000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>79000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3592,14 +3712,17 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,59 +3792,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5870000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6215000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6098000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6041000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5069000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5067000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5039000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4929000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4909000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5190000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5148000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4894000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4434000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4380800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4053300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3803200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3740,8 +3866,11 @@
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,59 +3924,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E57" s="3">
         <v>782000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>738000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>777000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>504000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>646000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>601000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>581000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>479000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>701000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>826000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>859000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>608000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>613300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>564900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>532500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3865,34 +3996,37 @@
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E58" s="3">
         <v>95000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>91000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>84000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>70000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>71000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>70000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>15000</v>
       </c>
       <c r="L58" s="3">
         <v>15000</v>
@@ -3913,11 +4047,11 @@
         <v>15000</v>
       </c>
       <c r="R58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S58" s="3">
         <v>13000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3936,59 +4070,62 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E59" s="3">
         <v>125000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>103000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>109000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>94000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>106000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>96000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>87000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>271000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>238000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>192000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>216000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>214300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>164900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>148600</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4007,59 +4144,62 @@
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1114000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1012000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1038000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>774000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>921000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>842000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>798000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>726000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>987000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1079000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1066000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>839000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>842600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>744800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>694100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4078,59 +4218,62 @@
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2415000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2542000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2550000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2546000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2001000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1566000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1683000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1694000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1444000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1537000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1592000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1510000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1456000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1459000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1462000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2251500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4149,59 +4292,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E62" s="3">
         <v>724000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>732000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>721000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>722000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>317000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>253000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>329000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>314000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>312000</v>
       </c>
       <c r="N62" s="3">
         <v>312000</v>
       </c>
       <c r="O62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="P62" s="3">
         <v>308000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>320500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>298500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>158500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4220,8 +4366,11 @@
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,59 +4588,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4096000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4465000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4378000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4397000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3545000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2852000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2826000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2737000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3162000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3486000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3598000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3458000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3109000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3157500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2981400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3104100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4504,8 +4662,11 @@
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,56 +4986,59 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E72" s="3">
         <v>433000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>385000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>284000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>189000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>491000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>447000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>403000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>458000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>404000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>298000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>180000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>92000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>44400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-20000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4880,14 +5054,17 @@
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,59 +5282,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1698000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1671000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1644000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1570000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1451000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1769000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1695000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1628000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1747000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1704000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1550000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1436000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1325000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1223300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1071900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>699100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5170,8 +5356,11 @@
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45592</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45501</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45410</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45319</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45228</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45137</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44955</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44864</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44682</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44591</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44409</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44318</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44136</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44045</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43954</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43863</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43772</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E81" s="3">
         <v>133000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>119000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>95000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>63000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>112000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>110000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>86000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>111000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>115000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>86000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>47700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>64400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,59 +5613,60 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7000</v>
       </c>
       <c r="H83" s="3">
         <v>7000</v>
       </c>
       <c r="I83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>37000</v>
       </c>
       <c r="M83" s="3">
         <v>37000</v>
       </c>
       <c r="N83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="O83" s="3">
         <v>36000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5486,8 +5685,11 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,59 +6055,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E89" s="3">
         <v>260000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>48000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>78000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>294000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>373000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>282000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>120000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>307000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>154000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-23000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-56600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-42500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5912,8 +6129,11 @@
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,59 +6159,60 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-5000</v>
       </c>
       <c r="L91" s="3">
         <v>-5000</v>
       </c>
       <c r="M91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6010,8 +6231,11 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,59 +6379,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-139000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-574000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-90000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-74000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-176000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3900</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6223,8 +6453,11 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6276,8 +6510,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6321,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,59 +6777,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-124000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>525000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-306000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-274000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-173000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-222000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-111000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-77000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>67000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>48000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>81400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-188000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6605,8 +6851,11 @@
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6631,8 +6880,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6676,59 +6925,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>81000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-176000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>177000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-253600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-60700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6745,6 +6997,9 @@
         <v>8</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,341 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E7" s="2">
         <v>45690</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45592</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45501</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45410</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45319</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45228</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45137</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44955</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44864</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44682</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44591</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44409</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44318</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44136</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44045</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43954</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43863</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43772</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1911000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1698000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2038000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1964000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1741000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1440000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1827000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1861000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1574000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1374000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1818000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1861000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1598000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1246500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1404800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1297600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1055000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>831800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1012500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>955900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>842100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>733200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>952100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1247000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1495000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1446000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1273000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1056000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1333000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1360000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1135000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1001000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1318000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1360000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1177000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>919100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1034200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>972400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>798000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>627600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>768100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>725300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>642900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>552400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>726100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E10" s="3">
         <v>451000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>543000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>518000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>468000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>384000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>494000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>501000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>439000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>373000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>500000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>501000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>421000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>327400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>370600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>325200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>257000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>204200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>244400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>230600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>199200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>180800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>226000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,8 +1030,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1091,8 +1105,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,8 +1182,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1203,24 +1223,24 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>300</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>300</v>
       </c>
       <c r="R14" s="3">
+        <v>300</v>
+      </c>
+      <c r="S14" s="3">
         <v>50400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1233,88 +1253,94 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E15" s="3">
         <v>48000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46000</v>
       </c>
       <c r="F15" s="3">
         <v>46000</v>
       </c>
       <c r="G15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H15" s="3">
         <v>43000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>37000</v>
       </c>
       <c r="J15" s="3">
         <v>37000</v>
       </c>
       <c r="K15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="L15" s="3">
         <v>35000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>35200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>33600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>34600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>33500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>32800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>33100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1740000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1574000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1815000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1760000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1573000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1324000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1610000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1635000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1393000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1250000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1584000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1624000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1418000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1138200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1257600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1248200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>986000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>799200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>947800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>896400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>813400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>712000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>898500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E18" s="3">
         <v>124000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>223000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>204000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>168000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>116000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>217000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>226000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>181000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>124000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>234000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>237000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>180000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>108300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>147200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>69000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>64700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>53600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,8 +1547,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1543,8 +1577,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1588,87 +1622,93 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E21" s="3">
         <v>172000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>269000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>250000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>211000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>154000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>254000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>263000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>216000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>162000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>271000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>274000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>216000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>146000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>184300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>86900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>106700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>65800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="E22" s="3">
         <v>36000</v>
@@ -1677,215 +1717,224 @@
         <v>36000</v>
       </c>
       <c r="G22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>36800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>36000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>35600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>33200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>33100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>29200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E23" s="3">
         <v>88000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>187000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>168000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>134000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>197000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>204000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>164000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>104000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>218000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>220000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>167000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>95600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>134200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>29100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E26" s="3">
         <v>67000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>140000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>126000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>101000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>158000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>164000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>133000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>84000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>178000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>182000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>137000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>78800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>109300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E27" s="3">
         <v>64000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>133000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>119000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>95000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>63000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>112000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>110000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>86000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>54000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>111000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>115000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>86000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>47700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>64400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2254,8 +2315,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,8 +2469,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2431,8 +2501,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2476,82 +2546,88 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E33" s="3">
         <v>64000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>133000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>119000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>95000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>63000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>112000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>110000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>86000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>111000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>115000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>86000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>47700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>64400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E35" s="3">
         <v>64000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>133000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>119000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>95000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>63000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>112000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>110000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>86000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>111000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>115000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>86000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>47700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>64400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E38" s="2">
         <v>45690</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45592</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45501</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45410</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45319</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45228</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45137</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44955</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44864</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44682</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44591</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44409</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44318</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44136</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44045</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43954</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43863</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43772</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,8 +2919,9 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2842,53 +2929,53 @@
         <v>8000</v>
       </c>
       <c r="E41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>177000</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
       <c r="O41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P41" s="3">
         <v>1000</v>
       </c>
       <c r="Q41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R41" s="3">
         <v>4900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>66600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>320200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2907,8 +2994,11 @@
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2981,62 +3071,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1066000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1378000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1294000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>973000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1215000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1231000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1098000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>955000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1273000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1264000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1113000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>884000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>946100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>832900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>716100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3055,62 +3148,65 @@
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1069000</v>
+      </c>
+      <c r="E44" s="3">
         <v>908000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>950000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>959000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>945000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>766000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>824000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>896000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1030000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1047000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1148000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1166000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1063000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>856000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>721200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>593200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>509200</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3129,8 +3225,11 @@
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3158,33 +3257,33 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>32000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3203,62 +3302,65 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2444000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2025000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2381000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2318000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2223000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1773000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2171000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2182000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2166000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2211000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2455000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2461000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2202000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1767000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1696900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1508300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1562800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3277,38 +3379,41 @@
       <c r="Z46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E47" s="3">
         <v>40000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>91000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>82000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>85000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>76000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3351,62 +3456,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E48" s="3">
         <v>412000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>387000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>369000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>366000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>343000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>326000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>314000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>299000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>280000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>268000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>267000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>252000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>246000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>249400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>226400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>227400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3425,62 +3533,65 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2833000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2848000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2797000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2816000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2345000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2334000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2363000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2334000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2330000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2359000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2351000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2361000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2386000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2414700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2314200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2013000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3499,8 +3610,11 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,59 +3764,62 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>88000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>108000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>69000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>79000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3715,14 +3835,17 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,62 +3918,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6278000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5870000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6215000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6098000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6041000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5069000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5067000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5039000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4929000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4909000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5190000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5148000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4894000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4434000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4380800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4053300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3803200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3869,8 +3995,11 @@
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,62 +4055,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>923000</v>
+      </c>
+      <c r="E57" s="3">
         <v>562000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>782000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>738000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>777000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>504000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>646000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>601000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>581000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>479000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>701000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>826000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>859000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>608000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>613300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>564900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>532500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3999,37 +4130,40 @@
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E58" s="3">
         <v>91000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>95000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>91000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>84000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>70000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>70000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>15000</v>
       </c>
       <c r="M58" s="3">
         <v>15000</v>
@@ -4050,11 +4184,11 @@
         <v>15000</v>
       </c>
       <c r="S58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="T58" s="3">
         <v>13000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4073,62 +4207,65 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E59" s="3">
         <v>90000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>125000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>103000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>109000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>94000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>106000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>96000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>87000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>232000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>271000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>238000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>192000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>216000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>214300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>164900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>148600</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4147,62 +4284,65 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E60" s="3">
         <v>866000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1114000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1012000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1038000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>774000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>921000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>842000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>798000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>726000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>987000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1079000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1066000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>839000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>842600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>744800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>694100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4221,62 +4361,65 @@
       <c r="Z60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2435000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2415000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2542000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2550000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2546000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2001000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1566000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1683000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1694000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1444000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1537000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1592000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1510000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1456000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1459000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1462000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2251500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4295,62 +4438,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E62" s="3">
         <v>728000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>724000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>732000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>721000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>722000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>317000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>253000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>205000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>329000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>314000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>312000</v>
       </c>
       <c r="O62" s="3">
         <v>312000</v>
       </c>
       <c r="P62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>308000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>320500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>298500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>158500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4369,8 +4515,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,62 +4746,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4457000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4096000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4465000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4378000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4397000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3545000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2852000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2826000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2737000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3162000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3486000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3598000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3458000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3109000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3157500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2981400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3104100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4665,8 +4823,11 @@
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5083,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,59 +5160,62 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E72" s="3">
         <v>449000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>433000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>385000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>284000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>189000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>491000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>447000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>403000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>458000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>404000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>298000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>180000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>92000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-20000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5057,14 +5231,17 @@
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,62 +5468,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1698000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1671000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1644000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1570000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1451000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1769000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1695000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1628000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1747000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1704000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1550000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1436000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1325000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1223300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1071900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>699100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5359,8 +5545,11 @@
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E80" s="2">
         <v>45690</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45592</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45501</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45410</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45319</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45228</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45137</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44955</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44864</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44682</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44591</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44409</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44318</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44136</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44045</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43954</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43863</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43772</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E81" s="3">
         <v>64000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>133000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>119000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>95000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>63000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>112000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>110000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>86000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>111000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>115000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>86000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>47700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>64400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,62 +5812,63 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E83" s="3">
         <v>9000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7000</v>
       </c>
       <c r="I83" s="3">
         <v>7000</v>
       </c>
       <c r="J83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K83" s="3">
         <v>8000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>37000</v>
       </c>
       <c r="N83" s="3">
         <v>37000</v>
       </c>
       <c r="O83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="P83" s="3">
         <v>36000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5688,8 +5887,11 @@
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,62 +6272,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E89" s="3">
         <v>235000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>260000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>78000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>294000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>373000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>282000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>120000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>307000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>154000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-56600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-42500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6132,8 +6349,11 @@
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,62 +6380,63 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-5000</v>
       </c>
       <c r="M91" s="3">
         <v>-5000</v>
       </c>
       <c r="N91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6234,8 +6455,11 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,62 +6609,65 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-139000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-574000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-88000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-90000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-74000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-176000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6456,8 +6686,11 @@
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,8 +6717,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6513,8 +6747,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6558,8 +6792,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,62 +7023,65 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-206000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-124000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>525000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-306000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-274000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-173000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-222000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-111000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-77000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>67000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>48000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>81400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-188000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6854,8 +7100,11 @@
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6883,8 +7132,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6928,62 +7177,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>81000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-176000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>177000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-61700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-253600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-60700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7000,6 +7252,9 @@
         <v>8</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,367 +656,379 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E7" s="2">
         <v>45872</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45781</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45690</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45592</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45501</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45410</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45319</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45228</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45137</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44955</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44864</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44682</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44591</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44409</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44318</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44136</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44045</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43954</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43863</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43772</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2062000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2093000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1911000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1698000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2038000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1964000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1741000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1440000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1827000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1861000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1574000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1374000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1818000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1861000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1598000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1246500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1404800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1297600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1055000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>831800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1012500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>955900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>842100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>733200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>952100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1501000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1533000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1401000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1247000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1495000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1446000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1273000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1056000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1333000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1360000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1135000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1001000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1318000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1360000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1177000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>919100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1034200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>972400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>798000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>627600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>768100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>725300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>642900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>552400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>726100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E10" s="3">
         <v>560000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>510000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>451000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>543000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>518000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>468000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>384000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>494000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>501000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>439000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>373000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>500000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>501000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>421000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>327400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>370600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>325200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>257000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>204200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>244400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>230600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>199200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>180800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>226000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1045,8 +1057,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1205,8 +1221,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1240,8 +1259,8 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1249,24 +1268,24 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>300</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>300</v>
       </c>
       <c r="T14" s="3">
+        <v>300</v>
+      </c>
+      <c r="U14" s="3">
         <v>50400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1279,94 +1298,100 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E15" s="3">
         <v>45000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>46000</v>
       </c>
       <c r="H15" s="3">
         <v>46000</v>
       </c>
       <c r="I15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J15" s="3">
         <v>43000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>38000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>37000</v>
       </c>
       <c r="L15" s="3">
         <v>37000</v>
       </c>
       <c r="M15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="N15" s="3">
         <v>35000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>36000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>35000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>35200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>33600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>34900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>33500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>32800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>33100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1392,168 +1417,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1880000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1740000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1574000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1815000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1760000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1573000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1324000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1610000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1635000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1393000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1250000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1584000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1624000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1418000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1138200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1257600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1248200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>986000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>799200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>947800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>896400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>813400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>712000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>898500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E18" s="3">
         <v>213000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>171000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>124000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>223000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>204000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>168000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>116000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>217000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>226000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>181000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>124000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>234000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>237000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>180000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>108300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>147200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>49400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>69000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>64700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>59500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>21200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>53600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1582,8 +1614,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1617,8 +1650,8 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1662,99 +1695,105 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E21" s="3">
         <v>258000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>217000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>172000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>269000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>250000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>211000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>154000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>254000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>263000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>216000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>162000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>271000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>274000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>216000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>146000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>184300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>86900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>106700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>65800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E22" s="3">
         <v>31000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>36000</v>
       </c>
       <c r="G22" s="3">
         <v>36000</v>
@@ -1763,227 +1802,236 @@
         <v>36000</v>
       </c>
       <c r="I22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="J22" s="3">
         <v>34000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>36800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>36000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>35600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>35000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>33200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>29200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E23" s="3">
         <v>182000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>141000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>88000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>187000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>168000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>134000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>197000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>204000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>164000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>104000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>218000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>220000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>167000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>95600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>134200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>24400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E24" s="3">
         <v>41000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>47000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>42000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>33000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>18000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>40000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>38000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>30000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2062,168 +2110,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E26" s="3">
         <v>141000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>105000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>67000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>140000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>126000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>76000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>158000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>164000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>133000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>84000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>178000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>182000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>137000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>78800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>109300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>24600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E27" s="3">
         <v>134000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>64000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>133000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>119000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>95000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>63000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>112000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>110000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>86000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>54000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>111000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>115000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>86000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>47700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>64400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>24600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2302,8 +2359,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2382,8 +2442,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2462,8 +2525,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2542,8 +2608,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2577,8 +2646,8 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2622,88 +2691,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E33" s="3">
         <v>134000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>64000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>133000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>119000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>95000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>63000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>112000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>110000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>86000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>54000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>111000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>115000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>86000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>47700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>64400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2782,173 +2857,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E35" s="3">
         <v>134000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>64000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>133000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>119000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>95000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>63000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>112000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>110000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>86000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>54000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>111000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>115000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>86000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>47700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>64400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E38" s="2">
         <v>45872</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45781</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45690</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45592</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45501</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45410</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45319</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45228</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45137</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44955</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44864</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44682</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44591</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44409</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44318</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44136</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44045</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43954</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43863</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43772</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2977,8 +3061,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3007,68 +3092,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E41" s="3">
         <v>25000</v>
-      </c>
-      <c r="E41" s="3">
-        <v>8000</v>
       </c>
       <c r="F41" s="3">
         <v>8000</v>
       </c>
       <c r="G41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H41" s="3">
         <v>10000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>177000</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <v>1000</v>
       </c>
       <c r="S41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T41" s="3">
         <v>4900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>66600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>320200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3087,17 +3173,20 @@
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E42" s="3">
         <v>22000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -3167,68 +3256,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1342000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1357000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1319000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1066000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1378000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1294000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>973000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1215000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1231000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1098000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>955000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1273000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1264000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1113000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>884000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>946100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>832900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>716100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3247,68 +3339,71 @@
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1056000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1069000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>908000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>950000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>959000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>945000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>766000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>824000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>896000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1030000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1047000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1148000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1166000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1063000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>856000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>721200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>593200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>509200</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3327,8 +3422,11 @@
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3362,33 +3460,33 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>32000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3407,68 +3505,71 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2507000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2510000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2444000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2025000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2381000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2318000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2223000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1773000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2171000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2182000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2166000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2211000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2455000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2461000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2202000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1767000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1696900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1508300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1562800</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3487,44 +3588,47 @@
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>28000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>91000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>82000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>85000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>76000</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
@@ -3567,68 +3671,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>455000</v>
+      </c>
+      <c r="E48" s="3">
         <v>450000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>439000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>412000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>387000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>369000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>366000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>343000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>326000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>314000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>299000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>280000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>268000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>267000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>252000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>246000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>249400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>226400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>227400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3647,8 +3754,11 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3656,59 +3766,59 @@
         <v>2765000</v>
       </c>
       <c r="E49" s="3">
+        <v>2765000</v>
+      </c>
+      <c r="F49" s="3">
         <v>2800000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2833000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2848000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2797000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2816000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2345000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2334000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2363000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2334000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2330000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2359000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2351000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2361000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2386000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2414700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2314200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2013000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3727,8 +3837,11 @@
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3807,8 +3920,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3887,8 +4003,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3896,56 +4015,56 @@
         <v>2000</v>
       </c>
       <c r="E52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>1000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>88000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>108000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>69000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>79000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3961,14 +4080,17 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4047,68 +4169,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6300000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6306000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6278000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5870000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6215000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6098000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6041000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5069000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5067000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5039000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4929000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4909000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5190000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5148000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4894000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4434000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4380800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4053300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3803200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4127,8 +4252,11 @@
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4157,8 +4285,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4187,68 +4316,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>734000</v>
+      </c>
+      <c r="E57" s="3">
         <v>758000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>923000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>562000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>782000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>738000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>777000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>504000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>646000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>601000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>581000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>479000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>701000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>826000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>859000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>608000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>613300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>564900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>532500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4267,8 +4397,11 @@
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4276,34 +4409,34 @@
         <v>120000</v>
       </c>
       <c r="E58" s="3">
+        <v>120000</v>
+      </c>
+      <c r="F58" s="3">
         <v>111000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>91000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>95000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>91000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>84000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>70000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>69000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>71000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>70000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>15000</v>
       </c>
       <c r="O58" s="3">
         <v>15000</v>
@@ -4324,11 +4457,11 @@
         <v>15000</v>
       </c>
       <c r="U58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="V58" s="3">
         <v>13000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4347,68 +4480,71 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E59" s="3">
         <v>145000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>144000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>90000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>125000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>103000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>109000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>94000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>106000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>96000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>87000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>232000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>271000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>238000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>192000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>216000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>214300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>164900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>148600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4427,68 +4563,71 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1117000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1246000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>866000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1114000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1012000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1038000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>774000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>921000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>842000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>798000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>726000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>987000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1079000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1066000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>839000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>842600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>744800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>694100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4507,68 +4646,71 @@
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2336000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2437000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2435000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2415000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2542000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2550000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2546000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2001000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1566000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1683000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1694000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1444000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1537000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1592000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1510000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1456000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1459000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1462000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2251500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4587,68 +4729,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E62" s="3">
         <v>702000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>689000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>728000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>724000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>732000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>721000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>722000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>317000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>253000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>205000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>329000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>314000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>312000</v>
       </c>
       <c r="Q62" s="3">
         <v>312000</v>
       </c>
       <c r="R62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="S62" s="3">
         <v>308000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>320500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>298500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>158500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4667,8 +4812,11 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4747,8 +4895,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4827,8 +4978,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4907,68 +5061,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4245000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4344000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4457000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4096000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4465000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4378000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4397000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3545000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2852000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2826000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2737000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3162000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3486000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3598000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3458000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3109000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3157500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2981400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3104100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4987,8 +5144,11 @@
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5017,8 +5177,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5097,8 +5258,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5177,8 +5341,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5257,8 +5424,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5337,65 +5507,68 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>736000</v>
+      </c>
+      <c r="E72" s="3">
         <v>642000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>515000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>449000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>433000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>385000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>284000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>189000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>491000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>447000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>403000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>458000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>404000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>298000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>180000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>92000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>44400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-20000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5411,14 +5584,17 @@
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5497,8 +5673,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5577,8 +5756,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5657,68 +5839,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1886000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1744000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1698000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1671000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1644000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1570000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1451000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1769000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1695000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1628000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1747000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1704000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1550000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1436000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1325000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1223300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1071900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>699100</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5737,8 +5922,11 @@
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5817,173 +6005,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E80" s="2">
         <v>45872</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45781</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45690</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45592</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45501</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45410</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45319</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45228</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45137</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44955</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44864</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44682</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44591</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44409</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44318</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44136</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44045</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43954</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43863</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43772</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E81" s="3">
         <v>134000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>64000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>133000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>119000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>95000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>63000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>112000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>110000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>86000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>54000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>111000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>115000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>86000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>47700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>64400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6012,68 +6209,69 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E83" s="3">
         <v>11000</v>
       </c>
       <c r="F83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G83" s="3">
         <v>9000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>7000</v>
       </c>
       <c r="K83" s="3">
         <v>7000</v>
       </c>
       <c r="L83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M83" s="3">
         <v>8000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>37000</v>
       </c>
       <c r="P83" s="3">
         <v>37000</v>
       </c>
       <c r="Q83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="R83" s="3">
         <v>36000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6092,8 +6290,11 @@
       <c r="AB83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6172,8 +6373,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6252,8 +6456,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6332,8 +6539,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6412,8 +6622,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6492,68 +6705,71 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E89" s="3">
         <v>34000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>77000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>235000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>260000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>48000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>78000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>294000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>373000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>282000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>120000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>307000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>154000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-56600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-42500</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6572,8 +6788,11 @@
       <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6602,68 +6821,69 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-5000</v>
       </c>
       <c r="O91" s="3">
         <v>-5000</v>
       </c>
       <c r="P91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6682,8 +6902,11 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +6985,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6842,68 +7068,71 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-574000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-88000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-74000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-77000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-176000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3900</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6922,8 +7151,11 @@
       <c r="AB94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6952,8 +7184,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6987,8 +7220,8 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -7032,8 +7265,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7112,8 +7348,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7192,8 +7431,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7272,68 +7514,71 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-61000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-206000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-124000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>525000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-306000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-274000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-222000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-111000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-77000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>67000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>48000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>81400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-188000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7352,8 +7597,11 @@
       <c r="AB100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7387,8 +7635,8 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -7432,68 +7680,71 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E102" s="3">
         <v>17000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-176000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>177000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-61700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-253600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-60700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7510,6 +7761,9 @@
         <v>8</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,379 +656,392 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E7" s="2">
         <v>45963</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45872</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45781</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45690</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45592</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45501</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45410</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45319</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45228</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45137</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44955</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44864</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44682</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44591</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44409</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44318</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44136</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44045</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43954</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43863</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43772</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1581000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2062000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2093000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1911000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1698000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2038000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1964000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1741000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1440000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1827000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1861000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1574000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1374000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1818000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1861000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1598000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1246500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1404800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1297600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1055000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>831800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1012500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>955900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>842100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>733200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>952100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>924000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1153000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1501000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1533000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1401000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1247000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1495000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1446000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1273000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1056000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1333000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1360000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1135000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1001000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1318000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1360000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1177000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>919100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1034200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>972400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>798000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>627600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>768100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>725300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>642900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>552400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>726100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E10" s="3">
         <v>561000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>560000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>510000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>451000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>543000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>518000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>468000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>384000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>494000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>501000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>439000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>373000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>500000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>501000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>421000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>327400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>370600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>325200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>257000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>204200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>244400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>230600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>199200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>180800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>226000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1058,8 +1071,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1141,8 +1155,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,8 +1241,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1262,8 +1282,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1271,24 +1291,24 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>300</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>300</v>
       </c>
       <c r="U14" s="3">
+        <v>300</v>
+      </c>
+      <c r="V14" s="3">
         <v>50400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1301,14 +1321,17 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1316,82 +1339,85 @@
         <v>46000</v>
       </c>
       <c r="E15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F15" s="3">
         <v>45000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46000</v>
       </c>
       <c r="I15" s="3">
         <v>46000</v>
       </c>
       <c r="J15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K15" s="3">
         <v>43000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>38000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>37000</v>
       </c>
       <c r="M15" s="3">
         <v>37000</v>
       </c>
       <c r="N15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="O15" s="3">
         <v>35000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>36000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>35400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>35200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>33600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>34600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>34300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>33500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>32800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>33100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1418,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1463000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1842000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1880000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1740000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1574000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1815000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1760000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1573000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1324000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1610000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1635000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1393000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1250000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1584000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1624000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1418000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1138200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1257600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1248200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>986000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>799200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>947800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>896400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>813400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>712000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>898500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>870900</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E18" s="3">
         <v>220000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>213000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>171000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>124000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>223000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>204000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>168000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>116000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>217000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>226000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>181000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>124000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>234000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>237000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>180000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>108300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>147200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>49400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>69000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>64700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>59500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>21200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>53600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1615,13 +1648,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-5000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1653,8 +1687,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1698,105 +1732,111 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E21" s="3">
         <v>266000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>258000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>217000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>172000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>269000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>250000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>211000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>154000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>254000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>263000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>216000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>162000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>271000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>274000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>216000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>146000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>184300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>86900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>106700</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>65800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E22" s="3">
         <v>30000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>36000</v>
       </c>
       <c r="H22" s="3">
         <v>36000</v>
@@ -1805,233 +1845,242 @@
         <v>36000</v>
       </c>
       <c r="J22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K22" s="3">
         <v>34000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>36800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>36000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>35300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>35600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>35000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>33100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>29200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E23" s="3">
         <v>190000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>182000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>141000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>88000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>187000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>168000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>134000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>197000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>204000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>164000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>104000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>218000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>220000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>167000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>95600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>134200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="3">
         <v>47000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>47000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>42000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>38000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>30000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2113,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E26" s="3">
         <v>143000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>141000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>105000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>140000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>126000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>101000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>76000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>158000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>164000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>133000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>84000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>178000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>182000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>137000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>78800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>109300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>24600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E27" s="3">
         <v>137000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>134000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>64000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>133000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>119000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>95000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>63000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>112000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>110000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>86000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>54000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>115000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>86000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>47700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>64400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>24600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2362,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2445,8 +2506,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2528,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2611,13 +2678,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>5000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -2649,8 +2719,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2694,91 +2764,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E33" s="3">
         <v>137000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>134000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>100000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>64000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>133000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>119000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>95000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>63000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>112000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>110000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>86000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>54000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>115000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>86000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>64400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>24600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2860,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E35" s="3">
         <v>137000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>134000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>100000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>64000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>133000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>119000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>95000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>63000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>112000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>110000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>86000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>54000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>115000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>86000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>64400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>24600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E38" s="2">
         <v>45963</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45872</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45781</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45690</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45592</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45501</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45410</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45319</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45228</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45137</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44955</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44864</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44682</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44591</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44409</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44318</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44136</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44045</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43954</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43863</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43772</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3062,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3093,71 +3179,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E41" s="3">
         <v>89000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25000</v>
-      </c>
-      <c r="F41" s="3">
-        <v>8000</v>
       </c>
       <c r="G41" s="3">
         <v>8000</v>
       </c>
       <c r="H41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177000</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
         <v>1000</v>
       </c>
       <c r="T41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U41" s="3">
         <v>4900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>66600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>320200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3176,20 +3263,23 @@
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="3">
         <v>16000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3259,71 +3349,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1342000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1357000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1319000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1066000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1378000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1294000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1200000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>973000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1215000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1231000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1098000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>955000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1273000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1264000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1113000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>884000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>946100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>832900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>716100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3342,71 +3435,74 @@
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>986000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1016000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1056000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1069000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>908000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>950000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>959000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>945000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>766000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>824000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>896000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1030000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1047000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1148000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1166000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1063000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>856000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>721200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>593200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>509200</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3425,8 +3521,11 @@
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3463,33 +3562,33 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>32000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3508,71 +3607,74 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2302000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2507000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2510000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2444000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2025000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2381000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2318000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2223000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1773000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2171000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2182000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2166000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2211000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2455000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2461000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2202000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1767000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1696900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1508300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1562800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3591,47 +3693,50 @@
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>6000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>28000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>44000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>66000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>82000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>85000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>76000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3674,71 +3779,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E48" s="3">
         <v>455000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>450000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>439000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>412000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>387000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>369000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>366000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>343000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>326000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>314000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>299000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>280000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>268000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>267000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>252000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>246000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>249400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>226400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>227400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3757,71 +3865,74 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2765000</v>
+        <v>2743000</v>
       </c>
       <c r="E49" s="3">
         <v>2765000</v>
       </c>
       <c r="F49" s="3">
+        <v>2765000</v>
+      </c>
+      <c r="G49" s="3">
         <v>2800000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2833000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2848000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2797000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2816000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2345000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2334000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2363000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2334000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2330000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2359000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2351000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2361000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2386000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2414700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2314200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2013000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3840,8 +3951,11 @@
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3923,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4006,68 +4123,71 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
       </c>
       <c r="F52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>88000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>108000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>69000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>79000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4400</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4083,14 +4203,17 @@
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4172,71 +4295,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6085000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6300000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6306000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6278000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5870000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6215000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6098000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6041000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5069000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5067000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5039000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4929000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4909000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5190000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5148000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4894000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4434000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4380800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4053300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3803200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4255,8 +4381,11 @@
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4286,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4317,71 +4447,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E57" s="3">
         <v>734000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>758000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>923000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>562000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>782000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>738000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>777000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>504000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>646000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>601000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>581000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>479000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>701000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>826000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>859000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>608000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>613300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>564900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>532500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4400,46 +4531,49 @@
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>120000</v>
+        <v>119000</v>
       </c>
       <c r="E58" s="3">
         <v>120000</v>
       </c>
       <c r="F58" s="3">
+        <v>120000</v>
+      </c>
+      <c r="G58" s="3">
         <v>111000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>91000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>95000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>91000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>84000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>70000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>69000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>71000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>70000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>15000</v>
       </c>
       <c r="P58" s="3">
         <v>15000</v>
@@ -4460,11 +4594,11 @@
         <v>15000</v>
       </c>
       <c r="V58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="W58" s="3">
         <v>13000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4483,71 +4617,74 @@
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E59" s="3">
         <v>146000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>144000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>125000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>103000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>109000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>94000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>106000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>96000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>87000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>232000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>271000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>238000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>192000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>216000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>214300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>164900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>148600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4566,71 +4703,74 @@
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>874000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1107000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1117000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1246000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>866000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1114000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1012000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1038000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>774000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>921000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>842000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>798000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>726000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>987000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1079000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1066000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>839000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>842600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>744800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>694100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4649,71 +4789,74 @@
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2338000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2336000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2437000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2435000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2415000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2542000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2550000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2546000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2001000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1566000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1683000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1694000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1444000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1537000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1592000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1510000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1456000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1459000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1462000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2251500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4732,71 +4875,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E62" s="3">
         <v>713000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>702000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>689000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>728000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>724000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>732000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>721000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>722000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>317000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>253000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>205000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>329000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>314000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>312000</v>
       </c>
       <c r="R62" s="3">
         <v>312000</v>
       </c>
       <c r="S62" s="3">
+        <v>312000</v>
+      </c>
+      <c r="T62" s="3">
         <v>308000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>320500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>298500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>158500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4815,8 +4961,11 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4898,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4981,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5064,71 +5219,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4011000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4245000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4344000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4457000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4096000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4465000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4378000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4397000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3545000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2852000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2826000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2737000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3162000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3486000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3598000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3458000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3109000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3157500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2981400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3104100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5147,8 +5305,11 @@
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5178,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5261,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5344,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5427,8 +5595,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5510,68 +5681,71 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E72" s="3">
         <v>736000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>642000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>515000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>449000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>433000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>385000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>284000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>189000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>491000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>447000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>403000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>458000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>404000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>298000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>180000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>92000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>44400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-20000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5587,14 +5761,17 @@
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB72" s="3">
-        <v>0</v>
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5676,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5759,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5842,71 +6025,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1997000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1977000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1886000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1744000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1698000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1671000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1644000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1570000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1451000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1769000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1695000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1628000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1747000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1550000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1436000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1325000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1223300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1071900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>699100</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5925,8 +6111,11 @@
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6008,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E80" s="2">
         <v>45963</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45872</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45781</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45690</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45592</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45501</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45410</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45319</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45228</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45137</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44955</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44864</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44682</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44591</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44409</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44318</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44136</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44045</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43954</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43863</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43772</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43681</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E81" s="3">
         <v>137000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>134000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>100000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>64000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>133000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>119000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>95000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>63000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>112000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>110000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>86000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>54000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>115000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>86000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>64400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>24600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6210,71 +6408,72 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E83" s="3">
         <v>10000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>11000</v>
       </c>
       <c r="F83" s="3">
         <v>11000</v>
       </c>
       <c r="G83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H83" s="3">
         <v>9000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>7000</v>
       </c>
       <c r="L83" s="3">
         <v>7000</v>
       </c>
       <c r="M83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N83" s="3">
         <v>8000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>37000</v>
       </c>
       <c r="Q83" s="3">
         <v>37000</v>
       </c>
       <c r="R83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="S83" s="3">
         <v>36000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6293,8 +6492,11 @@
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6376,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6459,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6542,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6625,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6708,71 +6922,74 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E89" s="3">
         <v>271000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>77000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>235000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>260000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>78000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>294000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>373000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>282000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>120000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>307000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>154000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-37000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-56600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-42500</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6791,8 +7008,11 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6822,71 +7042,72 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-5000</v>
       </c>
       <c r="P91" s="3">
         <v>-5000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6905,8 +7126,11 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6988,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7071,71 +7298,74 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-43000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-139000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-574000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-88000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-90000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-74000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-176000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3900</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7154,8 +7384,11 @@
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7185,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7223,8 +7457,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7268,8 +7502,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7351,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7434,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7517,71 +7760,74 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-164000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-61000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-206000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-124000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>525000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-306000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-274000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-173000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-222000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-111000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>67000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>48000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>81400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-188000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7600,8 +7846,11 @@
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7638,8 +7887,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7683,71 +7932,74 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E102" s="3">
         <v>64000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>81000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-176000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>177000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-61700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-253600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-60700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7764,6 +8016,9 @@
         <v>8</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
